--- a/backend/local_storage/users.xlsx
+++ b/backend/local_storage/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,21 +533,46 @@
           <t>kiranaglawe18@gmail.com</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>9766148444</t>
-        </is>
+      <c r="G3" t="n">
+        <v>9766148444</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>No one</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>00000000000</t>
-        </is>
-      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RV002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RV@002</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>employee</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Avinash Ganesh Chate</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
